--- a/Osorio_Ex3A_Tables.xlsx
+++ b/Osorio_Ex3A_Tables.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angelosorio\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BDB341C-CF1E-440D-AAA3-6BA1ABCAA14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A993F0-53D0-4F71-ABEB-739F1392476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{62CC3C23-3091-45CE-BC42-70C7076E2B0E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{62CC3C23-3091-45CE-BC42-70C7076E2B0E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Client" sheetId="1" r:id="rId1"/>
+    <sheet name="Dog" sheetId="2" r:id="rId2"/>
+    <sheet name="ClientService" sheetId="4" r:id="rId3"/>
+    <sheet name="DogService" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +38,70 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <si>
+    <t>Client_ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Dog _ID</t>
+  </si>
+  <si>
+    <t>Phone_Number</t>
+  </si>
+  <si>
+    <t>Dog_Name</t>
+  </si>
+  <si>
+    <t>Breed</t>
+  </si>
+  <si>
+    <t>Service_ID</t>
+  </si>
+  <si>
+    <t>Time_of_Service</t>
+  </si>
+  <si>
+    <t>Duration_Min</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Service ID</t>
+  </si>
+  <si>
+    <t>Dog ID</t>
+  </si>
+  <si>
+    <t>Polo</t>
+  </si>
+  <si>
+    <t>Pitbull</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -46,12 +111,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,8 +143,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +484,172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6218EF-A4EB-4E20-A28A-00B8CEF6B98F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>6304146577</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B264EBFA-9823-4653-9384-7F93924134BA}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7226AC67-007A-4247-A39B-BC086DA2D91B}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="3">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED5E8281-D50A-472F-955D-DEEBD933D14C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>